--- a/config/excel/rewards_v6_compact.xlsx
+++ b/config/excel/rewards_v6_compact.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH101"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2593,30 +2593,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>神圣守护</t>
+          <t>圣盾</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
         <v>4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>🛡️</t>
+          <t>😇</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>每关战斗开始时获得 1 层护盾，抵挡 1 次伤害（含致命）</t>
+          <t>每关开始获得 1 层圣盾，抵挡 1 次伤害（含致死）</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>6</v>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>每次连击 +2 枚手里剑/级 0.6×ATK</t>
+          <t>气力耗尽时，向斩击末端方向 spawn +2 枚手里剑/级 0.6×ATK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>每次划线结束，末端范围冲击 2.5×ATK，推开半径 200px (+0.3/级)</t>
+          <t>气力耗尽时，画线末端范围冲击 2.5×ATK，推开半径 200px (+0.3/级)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>画线轨迹首次闭合区间内：释放爆炸 3.0×ATK (+0.3/级)</t>
+          <t>气力耗尽且画线轨迹首次闭合时，闭合区间内释放爆炸 3.0×ATK (+0.3/级)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[2.5,2.0,600,"none","ranged_aoe",200,null]</t>
+          <t>[1.2,2.5,600,"none","ranged_aoe",200,null]</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -9645,6 +9645,990 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>demon_scythe</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>死神镰刀</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>气力耗尽时，画线末端释放无限射程贯通镰刀，4×ATK 伤害（最大生命 -30%）</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>46</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>[4.0,1]</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>trail</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>6</v>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S102" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="T102" s="3" t="inlineStr"/>
+      <c r="U102" s="3" t="inlineStr"/>
+      <c r="V102" s="3" t="inlineStr"/>
+      <c r="W102" s="3" t="inlineStr"/>
+      <c r="X102" s="3" t="inlineStr"/>
+      <c r="Y102" s="3" t="inlineStr"/>
+      <c r="Z102" s="3" t="inlineStr"/>
+      <c r="AA102" s="3" t="inlineStr"/>
+      <c r="AB102" s="3" t="inlineStr"/>
+      <c r="AC102" s="3" t="inlineStr"/>
+      <c r="AD102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>demon_sulfur_laser</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>硫磺火</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>10</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>每 4 秒释放跟随玩家的无限红色激光 1 秒，附加燃烧（最大生命 -30%）</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>47</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>[0.5,0.1,"fire"]</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>10</v>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="T103" s="3" t="inlineStr"/>
+      <c r="U103" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V103" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W103" s="3" t="inlineStr"/>
+      <c r="X103" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="Y103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z103" s="3" t="inlineStr"/>
+      <c r="AA103" s="3" t="inlineStr"/>
+      <c r="AB103" s="3" t="inlineStr"/>
+      <c r="AC103" s="3" t="inlineStr"/>
+      <c r="AD103" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>demon_baby</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>恶魔宝宝</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>10</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>召唤恶魔宝宝跟随玩家 远程激光穿透攻击 火伤（最大生命 -30%）</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>45</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>[1.5,1.2,600,"fire","ranged_laser",null,null]</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="S104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" s="3" t="inlineStr"/>
+      <c r="U104" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V104" s="3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="W104" s="3" t="inlineStr"/>
+      <c r="X104" s="3" t="inlineStr"/>
+      <c r="Y104" s="3" t="inlineStr"/>
+      <c r="Z104" s="3" t="inlineStr"/>
+      <c r="AA104" s="3" t="inlineStr"/>
+      <c r="AB104" s="3" t="inlineStr"/>
+      <c r="AC104" s="3" t="inlineStr"/>
+      <c r="AD104" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>demon_nine_lives</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>九命猫</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>10</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>九命：初始 1 命 + 8 次复活，复活后 HP=1（最大生命 -99%）</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>48</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>[8,1]</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>survive</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S105" s="3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="T105" s="3" t="inlineStr"/>
+      <c r="U105" s="3" t="inlineStr"/>
+      <c r="V105" s="3" t="inlineStr"/>
+      <c r="W105" s="3" t="inlineStr"/>
+      <c r="X105" s="3" t="inlineStr"/>
+      <c r="Y105" s="3" t="inlineStr"/>
+      <c r="Z105" s="3" t="inlineStr"/>
+      <c r="AA105" s="3" t="inlineStr"/>
+      <c r="AB105" s="3" t="inlineStr"/>
+      <c r="AC105" s="3" t="inlineStr"/>
+      <c r="AD105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>demon_vampire</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>吸血鬼</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>10</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>击杀时 5% 概率恢复 20% 最大生命（最大生命 -10%）</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>survive</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>3</v>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S106" s="3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="T106" s="3" t="inlineStr"/>
+      <c r="U106" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V106" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W106" s="3" t="inlineStr"/>
+      <c r="X106" s="3" t="inlineStr"/>
+      <c r="Y106" s="3" t="inlineStr"/>
+      <c r="Z106" s="3" t="inlineStr"/>
+      <c r="AA106" s="3" t="inlineStr"/>
+      <c r="AB106" s="3" t="inlineStr"/>
+      <c r="AC106" s="3" t="inlineStr"/>
+      <c r="AD106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>demon_blood_blade</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>血飞刀</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>10</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>👹</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>普攻改为血飞刀：穿透 + 射程 ×2 + 攻速 +100%，攻击 -80%（最大生命 -20%）</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>49</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>[1,2.0]</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S107" s="3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T107" s="3" t="inlineStr"/>
+      <c r="U107" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" s="3" t="inlineStr"/>
+      <c r="X107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Z107" s="3" t="inlineStr"/>
+      <c r="AA107" s="3" t="inlineStr"/>
+      <c r="AB107" s="3" t="inlineStr"/>
+      <c r="AC107" s="3" t="inlineStr"/>
+      <c r="AD107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>主题关专属（恶魔）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>angel_holy_bullet</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>圣光子弹</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>11</v>
+      </c>
+      <c r="D108" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>😇</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>普攻 10% 概率召唤光柱 AOE 雷伤</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>13</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>[0.1,0,2.0,150]</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>bullet</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>2</v>
+      </c>
+      <c r="R108" s="3" t="inlineStr"/>
+      <c r="S108" s="3" t="inlineStr"/>
+      <c r="T108" s="3" t="inlineStr"/>
+      <c r="U108" s="3" t="inlineStr"/>
+      <c r="V108" s="3" t="inlineStr"/>
+      <c r="W108" s="3" t="inlineStr"/>
+      <c r="X108" s="3" t="inlineStr"/>
+      <c r="Y108" s="3" t="inlineStr"/>
+      <c r="Z108" s="3" t="inlineStr"/>
+      <c r="AA108" s="3" t="inlineStr"/>
+      <c r="AB108" s="3" t="inlineStr"/>
+      <c r="AC108" s="3" t="inlineStr"/>
+      <c r="AD108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>主题关专属（天使）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>angel_light_ward</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>光之守护</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>11</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>😇</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>受到伤害 -50%</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>survive</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="S109" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T109" s="3" t="inlineStr"/>
+      <c r="U109" s="3" t="inlineStr"/>
+      <c r="V109" s="3" t="inlineStr"/>
+      <c r="W109" s="3" t="inlineStr"/>
+      <c r="X109" s="3" t="inlineStr"/>
+      <c r="Y109" s="3" t="inlineStr"/>
+      <c r="Z109" s="3" t="inlineStr"/>
+      <c r="AA109" s="3" t="inlineStr"/>
+      <c r="AB109" s="3" t="inlineStr"/>
+      <c r="AC109" s="3" t="inlineStr"/>
+      <c r="AD109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>主题关专属（天使）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>angel_baby</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>天使宝宝</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>11</v>
+      </c>
+      <c r="D110" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>😇</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>召唤天使宝宝跟随玩家 远程单体攻击 雷伤</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>45</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>[1.5,1.0,550,"thunder","ranged_single",null,null]</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>summon</t>
+        </is>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="S110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T110" s="3" t="inlineStr"/>
+      <c r="U110" s="3" t="inlineStr"/>
+      <c r="V110" s="3" t="inlineStr"/>
+      <c r="W110" s="3" t="inlineStr"/>
+      <c r="X110" s="3" t="inlineStr"/>
+      <c r="Y110" s="3" t="inlineStr"/>
+      <c r="Z110" s="3" t="inlineStr"/>
+      <c r="AA110" s="3" t="inlineStr"/>
+      <c r="AB110" s="3" t="inlineStr"/>
+      <c r="AC110" s="3" t="inlineStr"/>
+      <c r="AD110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>主题关专属（天使）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>angel_fate_spear</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>命运之矛</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>11</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>😇</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>环绕命运之矛 ×1</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>40</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>[1.5,0.4,"none",null,null,null]</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>sword</t>
+        </is>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R111" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="S111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" s="3" t="inlineStr"/>
+      <c r="U111" s="3" t="inlineStr"/>
+      <c r="V111" s="3" t="inlineStr"/>
+      <c r="W111" s="3" t="inlineStr"/>
+      <c r="X111" s="3" t="inlineStr"/>
+      <c r="Y111" s="3" t="inlineStr"/>
+      <c r="Z111" s="3" t="inlineStr"/>
+      <c r="AA111" s="3" t="inlineStr"/>
+      <c r="AB111" s="3" t="inlineStr"/>
+      <c r="AC111" s="3" t="inlineStr"/>
+      <c r="AD111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>主题关专属（天使）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>angel_proximity_slow</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>无下限术式</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>11</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>😇</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>玩家周围 300px 内怪物按距离线性减速，最高 50%</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>50</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>[300,0.5]</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="M112" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" s="3" t="inlineStr"/>
+      <c r="S112" s="3" t="inlineStr"/>
+      <c r="T112" s="3" t="inlineStr"/>
+      <c r="U112" s="3" t="inlineStr"/>
+      <c r="V112" s="3" t="inlineStr"/>
+      <c r="W112" s="3" t="inlineStr"/>
+      <c r="X112" s="3" t="inlineStr"/>
+      <c r="Y112" s="3" t="inlineStr"/>
+      <c r="Z112" s="3" t="inlineStr"/>
+      <c r="AA112" s="3" t="inlineStr"/>
+      <c r="AB112" s="3" t="inlineStr"/>
+      <c r="AC112" s="3" t="inlineStr"/>
+      <c r="AD112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>主题关专属（天使）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9656,7 +10640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10743,43 +11727,118 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>恶魔宝宝召唤数+</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>summon_demon_baby_count_add</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>恶魔宝宝（远程激光穿透）召唤数量</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>召唤</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>天使宝宝召唤数+</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>summon_angel_baby_count_add</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>天使宝宝（远程单体雷伤）召唤数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>剑</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>命运之矛数量+</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sword_spear_count_add</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>命运之矛（环绕长枪）数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1. 每个属性 base（一次性）+ per_lv（每级递增）共用同一 attr_id，分别写在「属性数值」「属性数值每级」列</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2. 自然上限 = base + per_lv × (max_level - 1)，无需在编码表 / Sheet1 单独表达</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>3. 单卡专属机制（穿障碍 / 弹射 / 分裂 / 镜像 / 复活 / Boss 满血 / 嘲讽 / 黑洞 等）不在本表，由 special_rule=1 + GDScript hand-code</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4. 元素状态（燃烧 / 减速 / 雷链 / 麻痹 / 中毒）的基础数值在 Sheet4 element_effects；单卡仅用 applies_&lt;elem&gt; 布尔标记是否触发</t>
+          <t>1. 每个属性 base（一次性）+ per_lv（每级递增）共用同一 attr_id，分别写在「属性数值」「属性数值每级」列</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
+        <is>
+          <t>2. 自然上限 = base + per_lv × (max_level - 1)，无需在编码表 / Sheet1 单独表达</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3. 单卡专属机制（穿障碍 / 弹射 / 分裂 / 镜像 / 复活 / Boss 满血 / 嘲讽 / 黑洞 等）不在本表，由 special_rule=1 + GDScript hand-code</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4. 元素状态（燃烧 / 减速 / 雷链 / 麻痹 / 中毒）的基础数值在 Sheet4 element_effects；单卡仅用 applies_&lt;elem&gt; 布尔标记是否触发</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>5. 元素覆盖 elem_&lt;type&gt;_attach_atk_mult（4 个，按元素选）仅当单卡需要偏离 Sheet4 base 时使用（如 orb_fire 想 burn 1.0×ATK）</t>
         </is>
@@ -11471,7 +12530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11597,1645 +12656,1790 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>恶魔</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>天使</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>2. rarity（品质编码 — 主表「品质」列）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>英文 key</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>中文</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>白</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>蓝</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>purple</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>紫</t>
+          <t>白</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>orange</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>橙</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>3. trigger_type（触发条件编码 — 主表「触发条件」列；条件数值/每级走「条件数值」/「条件数值每级」列）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>英文 key</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>passive</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>常驻</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>on_hit</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>受击时</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>on_kill</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>击杀时</t>
+          <t>常驻</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>on_pickup</t>
+          <t>on_hit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>拾取时</t>
+          <t>受击时</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>on_combo</t>
+          <t>on_kill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>每次连击时</t>
+          <t>击杀时</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>on_slash_end</t>
+          <t>on_pickup</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>划线斩击结束</t>
+          <t>拾取时</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>on_loop_close</t>
+          <t>on_combo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>轨迹首次闭合</t>
+          <t>每次连击时</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>on_death</t>
+          <t>on_slash_end</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>死亡时</t>
+          <t>划线斩击结束</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>stage_start</t>
+          <t>on_loop_close</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>每关开始</t>
+          <t>轨迹首次闭合</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>timer</t>
+          <t>on_death</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>定时器</t>
+          <t>死亡时</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>hp_below</t>
+          <t>stage_start</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HP 低于阈值（条件数值 = HP%）</t>
+          <t>每关开始</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vs_boss</t>
+          <t>timer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>对 Boss 战</t>
+          <t>定时器</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>stand</t>
+          <t>hp_below</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>站立达阈值（条件数值 = 秒）</t>
+          <t>HP 低于阈值（条件数值 = HP%）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>12</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>vs_boss</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>对 Boss 战</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>13</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>站立达阈值（条件数值 = 秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>14</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>combo_milestone</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>连击数达里程碑（条件数值 = 触发段位；条件数值每级 = 每级段位增量，-1 = 每级少 1 段）</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
         <is>
           <t>4. card_path（卡牌路径 — 主表「卡牌路径」列；前 7 个进伤害结算的「增伤层」按路径独立加和 dmg_&lt;path&gt;_pct，后 3 个不进结算）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>英文 key</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>物理（基础属性卡 / 受击触发等；进伤害结算）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>bullet</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>普攻子弹（进伤害结算）</t>
-        </is>
-      </c>
+      <c r="C42" s="1" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>combo</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>连击触发法术（进伤害结算）</t>
+          <t>物理（基础属性卡 / 受击触发等；进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>trail</t>
+          <t>bullet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>划线轨迹（进伤害结算）</t>
+          <t>普攻子弹（进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sword</t>
+          <t>combo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>环绕剑（进伤害结算）</t>
+          <t>连击触发法术（进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>summon</t>
+          <t>trail</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>召唤物（进伤害结算）</t>
+          <t>划线轨迹（进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>element</t>
+          <t>sword</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>元素附伤（具体元素由「附加燃烧/冰伤/雷链/中毒」布尔列决定；进伤害结算）</t>
+          <t>环绕剑（进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>survive</t>
+          <t>summon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>生存类（护盾/回血/减伤；不进伤害结算）</t>
+          <t>召唤物（进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>element</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>元规则类（球生成 / 拾取磁吸 / 纯属性 buff 等；不进伤害结算）</t>
+          <t>元素附伤（具体元素由「附加燃烧/冰伤/雷链/中毒」布尔列决定；进伤害结算）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>survive</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>生存类（护盾/回血/减伤；不进伤害结算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>元规则类（球生成 / 拾取磁吸 / 纯属性 buff 等；不进伤害结算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>debuff</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>仅施加 debuff（不直接造成伤害；不进伤害结算）</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>5. special_rule（专属规则编码 — 主表「专属规则」列；专属数值按本表 schema 顺序填，每级增量填「专属数值每级」列）</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>编码</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>英文 key</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>数组字段顺序</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>数组字段含义</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>0</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>无（纯属性）</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>无专属数值</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>on_hit_window</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>受击触发限时增伤</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[]（duration 走 attr 36）</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>无专属数值；持续秒走属性槽 duration_sec</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kill_stack</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>击杀叠层</t>
+          <t>无（纯属性）</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[stack_pct, max_stacks, duration_sec]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>每层攻击%；最大叠层数；叠层持续秒</t>
+          <t>无专属数值</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>aura</t>
+          <t>on_hit_window</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>光环易伤+伤害</t>
+          <t>受击触发限时增伤</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>[radius_px, tick_sec, atk_mult, vuln_per_lv]</t>
+          <t>[]（duration 走 attr 36）</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>光环半径(像素)；tick 间隔秒；每 tick 的 ATK 倍率；每级易伤增量</t>
+          <t>无专属数值；持续秒走属性槽 duration_sec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>boss_target</t>
+          <t>kill_stack</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boss 针对</t>
+          <t>击杀叠层</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>[boss_dmg_per_lv, heal_full_on_boss]</t>
+          <t>[stack_pct, max_stacks, duration_sec]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>对 Boss 每级增伤%；遇 Boss 是否满血(1/0)</t>
+          <t>每层攻击%；最大叠层数；叠层持续秒</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>trail_burn_walk</t>
+          <t>aura</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>火焰行走</t>
+          <t>光环易伤+伤害</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>[atk_mult, tick_sec, duration_sec]</t>
+          <t>[radius_px, tick_sec, atk_mult, vuln_per_lv]</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>脚下火地每 tick 的 ATK 倍率；tick 间隔秒；火地持续秒</t>
+          <t>光环半径(像素)；tick 间隔秒；每 tick 的 ATK 倍率；每级易伤增量</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>boss_target</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>护盾</t>
+          <t>Boss 针对</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>[charges, blocks_lethal, on_stage_start]</t>
+          <t>[boss_dmg_per_lv, heal_full_on_boss]</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>护盾层数；是否挡致死(1/0)；是否每关开始时给予(1/0)</t>
+          <t>对 Boss 每级增伤%；遇 Boss 是否满血(1/0)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>trail_burn_walk</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>复活</t>
+          <t>火焰行走</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>[revive_hp_pct, once_per_run]</t>
+          <t>[atk_mult, tick_sec, duration_sec]</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>复活时恢复 HP%；是否每局仅一次(1/0)</t>
+          <t>脚下火地每 tick 的 ATK 倍率；tick 间隔秒；火地持续秒</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>low_hp_regen</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>低血再生</t>
+          <t>护盾</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[hp_threshold, regen_pct_per_sec, regen_per_lv, target_hp_pct]</t>
+          <t>[charges, blocks_lethal, on_stage_start]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>触发的 HP 阈值；每秒回血%(基础)；每级回血%增量；最高回到的 HP%</t>
+          <t>护盾层数；是否挡致死(1/0)；是否每关开始时给予(1/0)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>stand_guard</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>站立减伤</t>
+          <t>复活</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[]（值在 attr/tv）</t>
+          <t>[revive_hp_pct, once_per_run]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>无专属数值；减伤%走属性槽，触发秒走 trigger_value</t>
+          <t>复活时恢复 HP%；是否每局仅一次(1/0)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>iframe_on_hit</t>
+          <t>low_hp_regen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>受击无敌</t>
+          <t>低血再生</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[iframe_sec]（CD 走 attr 35）</t>
+          <t>[hp_threshold, regen_pct_per_sec, regen_per_lv, target_hp_pct]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>无敌持续秒；冷却走属性槽 cooldown_sec</t>
+          <t>触发的 HP 阈值；每秒回血%(基础)；每级回血%增量；最高回到的 HP%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>bullet_distance_scale</t>
+          <t>stand_guard</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>元气弹</t>
+          <t>站立减伤</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[dmg_pct_max]</t>
+          <t>[]（值在 attr/tv）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>随飞行距离最高加成%</t>
+          <t>无专属数值；减伤%走属性槽，触发秒走 trigger_value</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bullet_homing</t>
+          <t>iframe_on_hit</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>追踪</t>
+          <t>受击无敌</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[homing_flag]</t>
+          <t>[iframe_sec]（CD 走 attr 35）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>是否追踪(1/0)</t>
+          <t>无敌持续秒；冷却走属性槽 cooldown_sec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>bullet_proc_spell</t>
+          <t>bullet_distance_scale</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>普攻概率触发法术</t>
+          <t>元气弹</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[proc_base, proc_per_lv, atk_mult, radius_px]</t>
+          <t>[dmg_pct_max]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>基础触发概率；每级概率增量；法术 ATK 倍率；法术半径(像素)</t>
+          <t>随飞行距离最高加成%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bullet_split</t>
+          <t>bullet_homing</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>命中分裂</t>
+          <t>追踪</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[count, atk_mult_base, atk_mult_per_lv]</t>
+          <t>[homing_flag]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>分裂出的子弹数；基础 ATK 倍率；每级倍率增量</t>
+          <t>是否追踪(1/0)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>bullet_bounce</t>
+          <t>bullet_proc_spell</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>弹射</t>
+          <t>普攻概率触发法术</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[bounce_per_lv, falloff]</t>
+          <t>[proc_base, proc_per_lv, atk_mult, radius_px]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>每级增加的弹射次数；每次弹射衰减(0~1)</t>
+          <t>基础触发概率；每级概率增量；法术 ATK 倍率；法术半径(像素)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>bullet_mirror</t>
+          <t>bullet_split</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>镜像回弹</t>
+          <t>命中分裂</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[return_atk_mult]</t>
+          <t>[count, atk_mult_base, atk_mult_per_lv]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>回弹弹的 ATK 倍率</t>
+          <t>分裂出的子弹数；基础 ATK 倍率；每级倍率增量</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>bullet_side</t>
+          <t>bullet_bounce</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>斜射</t>
+          <t>弹射</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[count, angle_deg]</t>
+          <t>[bounce_per_lv, falloff]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>斜射子弹数；左右偏移角度</t>
+          <t>每级增加的弹射次数；每次弹射衰减(0~1)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bullet_beam</t>
+          <t>bullet_mirror</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>能量光束</t>
+          <t>镜像回弹</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>[proc_base, proc_per_lv, atk_mult, pierce]</t>
+          <t>[return_atk_mult]</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>基础触发概率；每级概率增量；光束 ATK 倍率；是否穿透(1/0)</t>
+          <t>回弹弹的 ATK 倍率</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>combo_count_mult</t>
+          <t>bullet_side</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>造成连击数翻倍</t>
+          <t>斜射</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>[combo_gain_mult]</t>
+          <t>[count, angle_deg]</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>单次斩击产生的连击数倍率(2.0 = 双倍连击)</t>
+          <t>斜射子弹数；左右偏移角度</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>combo_milestone_spell</t>
+          <t>bullet_beam</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>连击里程碑法术</t>
+          <t>能量光束</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>[shape, radius_px, extra_blade_per_lv]（shape ∈ line/circle/point）</t>
+          <t>[proc_base, proc_per_lv, atk_mult, pierce]</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>形状(line/circle/point)；半径(像素，0=不适用)；每级追加刀数(空=不用)</t>
+          <t>基础触发概率；每级概率增量；光束 ATK 倍率；是否穿透(1/0)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>combo_charge</t>
+          <t>combo_count_mult</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>蓄力击</t>
+          <t>造成连击数翻倍</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>[charge_per_04s_pct, charge_max_mult]</t>
+          <t>[combo_gain_mult]</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>每 0.4s 蓄力增伤%；蓄满最大倍率</t>
+          <t>单次斩击产生的连击数倍率(2.0 = 双倍连击)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>combo_shuriken</t>
+          <t>combo_milestone_spell</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>连击辅助子弹</t>
+          <t>连击里程碑法术</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[shape, random_dir]</t>
+          <t>[shape, radius_px, extra_blade_per_lv]（shape ∈ line/circle/point）</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>形状(line/circle 等)；是否随机方向(1/0)</t>
+          <t>形状(line/circle/point)；半径(像素，0=不适用)；每级追加刀数(空=不用)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>combo_crit</t>
+          <t>combo_charge</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>连击里程碑暴击</t>
+          <t>蓄力击</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[combo_step]</t>
+          <t>[charge_per_04s_pct, charge_max_mult]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>每多少连击数触发一次必暴</t>
+          <t>每 0.4s 蓄力增伤%；蓄满最大倍率</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>trail_extra</t>
+          <t>combo_shuriken</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>多重轨迹</t>
+          <t>连击辅助子弹</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[extra_count]</t>
+          <t>[shape, random_dir]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>额外轨迹条数</t>
+          <t>形状(line/circle 等)；是否随机方向(1/0)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>trail_elem_field</t>
+          <t>combo_crit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>元素轨迹场域</t>
+          <t>连击里程碑暴击</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[atk_mult, tick_sec, slow_pct, stun_sec, ramp_per_sec, bullet_attach]</t>
+          <t>[combo_step]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>每 tick 的 ATK 倍率；tick 间隔秒；override 减速%(空=用Sheet4)；眩晕秒；每秒伤害爬升%；是否让子弹附状态(1/0)</t>
+          <t>每多少连击数触发一次必暴</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>trail_endwave</t>
+          <t>trail_extra</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>划线末端推开</t>
+          <t>多重轨迹</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[radius_base, radius_per_lv]</t>
+          <t>[extra_count]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>基础推开半径(像素)；每级半径增量(像素)</t>
+          <t>额外轨迹条数</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>trail_loop_explode</t>
+          <t>trail_elem_field</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>闭合爆炸</t>
+          <t>元素轨迹场域</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[weapon_mult_per_lv, min_area]</t>
+          <t>[atk_mult, tick_sec, slow_pct, stun_sec, ramp_per_sec, bullet_attach]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>每级闭合爆炸的武器倍率增量；触发的最小闭合面积</t>
+          <t>每 tick 的 ATK 倍率；tick 间隔秒；override 减速%(空=用Sheet4)；眩晕秒；每秒伤害爬升%；是否让子弹附状态(1/0)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>trail_pierce</t>
+          <t>trail_endwave</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>穿障碍</t>
+          <t>划线末端推开</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[pierce_obstacles]</t>
+          <t>[radius_base, radius_per_lv]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>是否穿障碍(1/0)</t>
+          <t>基础推开半径(像素)；每级半径增量(像素)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>trail_width_buff</t>
+          <t>trail_loop_explode</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>轨迹宽度</t>
+          <t>闭合爆炸</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[width_pct_per_lv]</t>
+          <t>[weapon_mult_per_lv, min_area]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>每级轨迹宽度%</t>
+          <t>每级闭合爆炸的武器倍率增量；触发的最小闭合面积</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>trail_dmg_buff</t>
+          <t>trail_pierce</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>轨迹伤害</t>
+          <t>穿障碍</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[dmg_pct_per_lv]</t>
+          <t>[pierce_obstacles]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>每级轨迹伤害%</t>
+          <t>是否穿障碍(1/0)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>orb_spawn</t>
+          <t>trail_width_buff</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>球生成间隔</t>
+          <t>轨迹宽度</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[spawn_interval_base, spawn_interval_per_lv]</t>
+          <t>[width_pct_per_lv]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>基础生成间隔秒；每级间隔变化秒(负=变快)</t>
+          <t>每级轨迹宽度%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>orb_mark</t>
+          <t>trail_dmg_buff</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>球印记复制</t>
+          <t>轨迹伤害</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[dup_chance_base, dup_chance_per_lv]</t>
+          <t>[dmg_pct_per_lv]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>基础复制概率；每级概率增量</t>
+          <t>每级轨迹伤害%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>orb_field</t>
+          <t>orb_spawn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>场上球数量</t>
+          <t>球生成间隔</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[count_pct_per_lv]</t>
+          <t>[spawn_interval_base, spawn_interval_per_lv]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>每级场上球数%增量</t>
+          <t>基础生成间隔秒；每级间隔变化秒(负=变快)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>orb_magnet</t>
+          <t>orb_mark</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>球磁吸</t>
+          <t>球印记复制</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[pickup_radius_pct_per_lv, line_magnet_pct_per_lv]</t>
+          <t>[dup_chance_base, dup_chance_per_lv]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>每级拾取半径%；每级划线吸附%</t>
+          <t>基础复制概率；每级概率增量</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>orb_burst</t>
+          <t>orb_field</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>拾取爆炸</t>
+          <t>场上球数量</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[weapon_mult]</t>
+          <t>[count_pct_per_lv]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>拾取爆炸的武器倍率</t>
+          <t>每级场上球数%增量</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>orb_glow</t>
+          <t>orb_magnet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>球之微光</t>
+          <t>球磁吸</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[dmg_pct_per_lv]（duration 在 attr 36）</t>
+          <t>[pickup_radius_pct_per_lv, line_magnet_pct_per_lv]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>每级增伤%；持续秒走属性槽 duration_sec</t>
+          <t>每级拾取半径%；每级划线吸附%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>orb_elem_aoe</t>
+          <t>orb_burst</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>元素球 AOE</t>
+          <t>拾取爆炸</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[weapon_mult, element]（元素状态由 Sheet4 自动应用）</t>
+          <t>[weapon_mult]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AOE 武器倍率；元素 key(fire/ice/thunder/poison)</t>
+          <t>拾取爆炸的武器倍率</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>sword_count_mult</t>
+          <t>orb_glow</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>剑数翻倍</t>
+          <t>球之微光</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[count_mult]</t>
+          <t>[dmg_pct_per_lv]（duration 在 attr 36）</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>总剑数倍率</t>
+          <t>每级增伤%；持续秒走属性槽 duration_sec</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sword_proc_spell</t>
+          <t>orb_elem_aoe</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>剑触发法术</t>
+          <t>元素球 AOE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[proc_chance, atk_mult, radius_per_lv]</t>
+          <t>[weapon_mult, element]（元素状态由 Sheet4 自动应用）</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>触发概率；法术 ATK 倍率；每级法术半径增量</t>
+          <t>AOE 武器倍率；元素 key(fire/ice/thunder/poison)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>sword_unit</t>
+          <t>sword_count_mult</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>剑单位（典型剑）</t>
+          <t>剑数翻倍</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[atk_mult, hit_interval_sec, element, p1, p2, p3] / p1-3 仅用于守护剑 block_bullets 或 override Sheet4；元素自带状态由 Sheet4 自动应用</t>
+          <t>[count_mult]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ATK 倍率；命中间隔秒；元素(none/fire/ice/thunder/poison)；p1-p3 仅守护剑用(block_bullets)或 override Sheet4 base</t>
+          <t>总剑数倍率</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>sword_length_buff</t>
+          <t>sword_proc_spell</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>剑长度</t>
+          <t>剑触发法术</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[length_pct_per_lv]</t>
+          <t>[proc_chance, atk_mult, radius_per_lv]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>每级剑长度%</t>
+          <t>触发概率；法术 ATK 倍率；每级法术半径增量</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>sword_speed_buff</t>
+          <t>sword_unit</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>剑转速</t>
+          <t>剑单位（典型剑）</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[speed_pct_per_lv]</t>
+          <t>[atk_mult, hit_interval_sec, element, p1, p2, p3] / p1-3 仅用于守护剑 block_bullets 或 override Sheet4；元素自带状态由 Sheet4 自动应用</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>每级剑转速%</t>
+          <t>ATK 倍率；命中间隔秒；元素(none/fire/ice/thunder/poison)；p1-p3 仅守护剑用(block_bullets)或 override Sheet4 base</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>sword_dmg_buff</t>
+          <t>sword_length_buff</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>剑伤害</t>
+          <t>剑长度</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[dmg_pct_per_lv]</t>
+          <t>[length_pct_per_lv]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>每级剑伤害%</t>
+          <t>每级剑长度%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>summon_pact</t>
+          <t>sword_speed_buff</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>召唤盟约</t>
+          <t>剑转速</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[summon_size_pct, summon_atk_speed_pct]</t>
+          <t>[speed_pct_per_lv]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>召唤物体型%；召唤物攻速%（解锁的单位走属性槽 summon_*_count_add += 1 表达，与其他召唤卡一致）</t>
+          <t>每级剑转速%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
+        <v>43</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>sword_dmg_buff</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>剑伤害</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[dmg_pct_per_lv]</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>每级剑伤害%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>44</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>summon_pact</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>召唤盟约</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[summon_size_pct, summon_atk_speed_pct]</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>召唤物体型%；召唤物攻速%（解锁的单位走属性槽 summon_*_count_add += 1 表达，与其他召唤卡一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
         <v>45</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>summon_unit</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>召唤单位</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>[atk_mult, atk_interval_sec, range_px, element, mechanic, p1, p2] / mechanic ∈ ranged_single/ranged_aoe/ranged_taunt/random_aoe；p1-2 仅用于 ranged_aoe 的 radius_px 或 ranged_taunt 的 cd/duration；元素自带状态由 Sheet4 自动应用</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ATK 倍率；攻击间隔秒；攻击距离(像素)；元素；机制(ranged_single/ranged_aoe/ranged_taunt/random_aoe)；p1=AOE 半径或嘲讽 CD；p2=嘲讽持续秒</t>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[atk_mult, atk_interval_sec, range_px, element, mechanic, p1, p2] / mechanic ∈ ranged_single/ranged_aoe/ranged_taunt/random_aoe/ranged_laser；p1-2 仅用于 ranged_aoe 的 radius_px 或 ranged_taunt 的 cd/duration；ranged_laser = 持续穿透激光（无 p1/p2）；元素自带状态由 Sheet4 自动应用</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ATK 倍率；攻击间隔秒；攻击距离(像素)；元素；机制(ranged_single/ranged_aoe/ranged_taunt/random_aoe/ranged_laser)；p1=AOE 半径或嘲讽 CD；p2=嘲讽持续秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>46</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>scythe_on_slash_end</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>死神镰刀（划线末释放无限射程贯通镰刀）</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[atk_mult, pierce]</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>镰刀 ATK 倍率；是否贯通(1/0)；射程无限</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>47</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>periodic_laser</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>硫磺火（定时无限激光）</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[atk_mult_per_tick, tick_interval_sec, element]</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>激光每 tick 的 ATK 倍率；tick 间隔秒；元素 key(fire/ice/thunder/poison)；冷却走属性槽 cooldown_sec；持续走 duration_sec；元素状态由 Sheet4 自动应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>48</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>multi_revive</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>多命复活（九命猫）</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[extra_lives, max_hp_after_revive_abs]</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>额外复活次数（初始 1 命之外）；复活后绝对 HP 值（1 = 1HP）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>49</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>blood_bullet</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>血飞刀（普攻替换为穿透血刃）</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[pierce, range_mult]</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>是否穿透(1/0)；射程倍率；攻速/攻击调整走属性槽 atk_speed_pct / atk_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>50</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>proximity_slow</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>无下限术式（近距离怪物线性减速）</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[aura_radius_px, max_slow_pct]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>光环半径(像素)；最大减速%（距离玩家越近减速越高，线性插值）</t>
         </is>
       </c>
     </row>

--- a/config/excel/rewards_v6_compact.xlsx
+++ b/config/excel/rewards_v6_compact.xlsx
@@ -2883,7 +2883,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>走过留下火焰 0.15×ATK/0.5s 伤害（持续 2s），附加燃烧</t>
+          <t>走过留下火焰 0.15×ATK/0.5s 伤害（持续 4s），附加燃烧</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2897,8 +2897,11 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[0.15,0.5,2]</t>
-        </is>
+          <t>[0.15,0.5,4]</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2957,7 +2960,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Footprints deal 0.15×ATK/0.5s for 2s, ignites burn</t>
+          <t>Footprints deal 0.15×ATK/0.5s for 4s, ignites burn</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -12825,7 +12828,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
         <v>54</v>
